--- a/base/StructureDefinition-SGStructureDefinition.xlsx
+++ b/base/StructureDefinition-SGStructureDefinition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="395">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}sdf-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}sdf-1:Element paths must be unique unless the structure is a constraint {derivation = 'constraint' or snapshot.element.select(path).isDistinct()}sdf-15a:If the first element in a differential has no "." in the path and it's not a logical model, it has no type {(kind!='logical'  and differential.element.first().path.contains('.').not()) implies differential.element.first().type.empty()}sdf-4:If the structure is not abstract, then there SHALL be a baseDefinition {abstract = true or baseDefinition.exists()}sdf-5:If the structure defines an extension then the structure must have context information {type != 'Extension' or derivation = 'specialization' or (context.exists())}sdf-6:A structure must have either a differential, or a snapshot (or both) {snapshot.exists() or differential.exists()}sdf-9:In any snapshot or differential, no label, code or requirements on an element without a "." in the path (e.g. the first element) {children().element.where(path.contains('.').not()).label.empty() and children().element.where(path.contains('.').not()).code.empty() and children().element.where(path.contains('.').not()).requirements.empty()}sdf-11:If there's a type, its content must match the path name in the first element of a snapshot {kind != 'logical' implies snapshot.empty() or snapshot.element.first().path = type}sdf-14:All element definitions must have an id {snapshot.element.all(id.exists()) and differential.element.all(id.exists())}sdf-15:The first element in a snapshot has no type unless model is a logical model. {kind!='logical' implies snapshot.element.first().type.empty()}sdf-16:All element definitions must have unique ids (snapshot) {snapshot.element.all(id.exists()) and snapshot.element.id.trace('ids').isDistinct()}sdf-17:All element definitions must have unique ids (diff) {differential.element.all(id.exists()) and differential.element.id.trace('ids').isDistinct()}sdf-18:Context Invariants can only be used for extensions {contextInvariant.exists() implies type = 'Extension'}sdf-19:FHIR Specification models only use FHIR defined types {url.startsWith('http://hl7.org/fhir/StructureDefinition') implies (differential.element.type.code.all(matches('^[a-zA-Z0-9]+$') or matches('^http:\\/\\/hl7\\.org\\/fhirpath\\/System\\.[A-Z][A-Za-z]+$')) and snapshot.element.type.code.all(matches('^[a-zA-Z0-9\\.]+$') or matches('^http:\\/\\/hl7\\.org\\/fhirpath\\/System\\.[A-Z][A-Za-z]+$')))}sdf-21:Default values can only be specified on specializations {differential.element.defaultValue.exists() implies (derivation = 'specialization')}sdf-22:FHIR Specification models never have default values {url.startsWith('http://hl7.org/fhir/StructureDefinition') implies (snapshot.element.defaultValue.empty() and differential.element.defaultValue.empty())}sdf-23:No slice name on root {(snapshot | differential).element.all(path.contains('.').not() implies sliceName.empty())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}sdf-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}sdf-1:Element paths must be unique unless the structure is a constraint {derivation = 'constraint' or snapshot.element.select(path).isDistinct()}sdf-15a:If the first element in a differential has no "." in the path and it's not a logical model, it has no type {(kind!='logical'  and differential.element.first().path.contains('.').not()) implies differential.element.first().type.empty()}sdf-4:If the structure is not abstract, then there SHALL be a baseDefinition {abstract = true or baseDefinition.exists()}sdf-5:If the structure defines an extension then the structure must have context information {type != 'Extension' or derivation = 'specialization' or (context.exists())}sdf-6:A structure must have either a differential, or a snapshot (or both) {snapshot.exists() or differential.exists()}sdf-9:In any snapshot or differential, no label, code or requirements on an element without a "." in the path (e.g. the first element) {children().element.where(path.contains('.').not()).label.empty() and children().element.where(path.contains('.').not()).code.empty() and children().element.where(path.contains('.').not()).requirements.empty()}sdf-11:If there's a type, its content must match the path name in the first element of a snapshot {kind != 'logical' implies snapshot.empty() or snapshot.element.first().path = type}sdf-14:All element definitions must have an id {snapshot.element.all(id.exists()) and differential.element.all(id.exists())}sdf-15:The first element in a snapshot has no type unless model is a logical model. {kind!='logical' implies snapshot.element.first().type.empty()}sdf-16:All element definitions must have unique ids (snapshot) {snapshot.element.all(id.exists()) and snapshot.element.id.trace('ids').isDistinct()}sdf-17:All element definitions must have unique ids (diff) {differential.element.all(id.exists()) and differential.element.id.trace('ids').isDistinct()}sdf-18:Context Invariants can only be used for extensions {contextInvariant.exists() implies type = 'Extension'}sdf-19:FHIR Specification models only use FHIR defined types {url.startsWith('http://hl7.org/fhir/StructureDefinition') implies (differential.element.type.code.all(matches('^[a-zA-Z0-9]+$') or matches('^http:\\/\\/hl7\\.org\\/fhirpath\\/System\\.[A-Z][A-Za-z]+$')) and snapshot.element.type.code.all(matches('^[a-zA-Z0-9\\.]+$') or matches('^http:\\/\\/hl7\\.org\\/fhirpath\\/System\\.[A-Z][A-Za-z]+$')))}sdf-21:Default values can only be specified on specializations {differential.element.defaultValue.exists() implies (derivation = 'specialization')}sdf-22:FHIR Specification models never have default values {url.startsWith('http://hl7.org/fhir/StructureDefinition') implies (snapshot.element.defaultValue.empty() and differential.element.defaultValue.empty())}sdf-23:No slice name on root {(snapshot | differential).element.all(path.contains('.').not() implies sliceName.empty())}shr-1:If knowledge capabilities are stated, they SHALL include shareable {extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').exists() implies extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').where(value = 'shareable').exists()}</t>
   </si>
   <si>
     <t>n/a</t>
@@ -365,7 +365,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -466,20 +466,8 @@
     <t>Defines a knowledge capability afforded by this knowledge artifact.</t>
   </si>
   <si>
-    <t>StructureDefinition.extension:artifactComment</t>
-  </si>
-  <si>
-    <t>artifactComment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {cqf-artifactComment}
-</t>
-  </si>
-  <si>
-    <t>Additional documentation, review, or usage guidance</t>
-  </si>
-  <si>
-    <t>A comment containing additional documentation, a review comment, usage guidance, or other relevant information from a particular user.</t>
+    <t>ele-1
+shr-1</t>
   </si>
   <si>
     <t>StructureDefinition.extension:versionAlgorithm</t>
@@ -501,6 +489,10 @@
     <t>If set as a string, this is a FHIRPath expression that has two additional context variables passed in - %version1 and %version2 and will return a negative number if version1 is newer, a positive number if version2 and a 0 if the version ordering can't be successfully be determined.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>StructureDefinition.extension:versionPolicy</t>
   </si>
   <si>
@@ -515,6 +507,22 @@
   </si>
   <si>
     <t>Defines the versioning policy of the artifact.</t>
+  </si>
+  <si>
+    <t>StructureDefinition.extension:webSource</t>
+  </si>
+  <si>
+    <t>webSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {web-source}
+</t>
+  </si>
+  <si>
+    <t>web-source</t>
+  </si>
+  <si>
+    <t>Where a human readable web page describing the resource can be found, if it's at a different location to the canonical URL itself.</t>
   </si>
   <si>
     <t>StructureDefinition.modifierExtension</t>
@@ -839,7 +847,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -901,7 +909,7 @@
     <t>Codes for the meaning of the defined structure (SNOMED CT and LOINC codes, as an example).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-use</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-use|4.0.1</t>
   </si>
   <si>
     <t>keywords</t>
@@ -1134,7 +1142,7 @@
     <t>Either a resource or a data type, including logical model types.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/defined-types</t>
+    <t>http://hl7.org/fhir/ValueSet/defined-types|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">sdf-11
@@ -1144,7 +1152,7 @@
     <t>StructureDefinition.baseDefinition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1170,7 +1178,7 @@
     <t>How the type relates to the baseDefinition.</t>
   </si>
   <si>
-    <t>If the definition is a specialization, then it adds new elements in the differential, and the snapshot includes the inherited elements.  If the definition is a constraint, then it cannot define new elements, it can only make new rules about existing content (see [Profiling Resources](http://hl7.org/fhir/uv/crmi/STU1/profiling.html#resources)).</t>
+    <t>If the definition is a specialization, then it adds new elements in the differential, and the snapshot includes the inherited elements.  If the definition is a constraint, then it cannot define new elements, it can only make new rules about existing content (see [Profiling Resources](http://hl7.org/fhir/R4/profiling.html#resources)).</t>
   </si>
   <si>
     <t>How a type relates to its baseDefinition.</t>
@@ -1571,17 +1579,17 @@
   <dimension ref="A1:AO61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.7109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.57421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.96484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.66796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="34.17578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="30.79296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1590,27 +1598,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="85.85546875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.4375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="36.703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="76.2421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.05859375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="31.90234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.67578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="18.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2666,7 +2674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2762,7 +2770,7 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>138</v>
@@ -2783,15 +2791,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -2801,7 +2809,7 @@
         <v>83</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>88</v>
@@ -2813,15 +2821,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2879,7 +2889,7 @@
         <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>138</v>
@@ -2902,13 +2912,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -2921,7 +2931,7 @@
         <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -2930,17 +2940,15 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2998,7 +3006,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>138</v>
@@ -3019,15 +3027,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -3049,13 +3057,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3115,7 +3123,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>138</v>
@@ -3138,14 +3146,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3167,16 +3175,16 @@
         <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3225,7 +3233,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>83</v>
@@ -3255,16 +3263,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3286,16 +3294,16 @@
         <v>101</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3344,7 +3352,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3362,10 +3370,10 @@
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3376,10 +3384,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3402,19 +3410,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3463,7 +3471,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -3481,24 +3489,24 @@
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3521,16 +3529,16 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3580,7 +3588,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>83</v>
@@ -3598,10 +3606,10 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
@@ -3610,12 +3618,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3638,19 +3646,19 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3699,7 +3707,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3708,7 +3716,7 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>99</v>
@@ -3729,12 +3737,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3757,16 +3765,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3816,7 +3824,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -3834,7 +3842,7 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -3846,12 +3854,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3877,13 +3885,13 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3909,13 +3917,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3933,7 +3941,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3951,24 +3959,24 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3991,19 +3999,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4052,7 +4060,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -4070,28 +4078,28 @@
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4110,16 +4118,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4169,7 +4177,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4187,10 +4195,10 @@
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4199,12 +4207,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4227,19 +4235,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4288,7 +4296,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -4306,24 +4314,24 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4346,16 +4354,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4405,7 +4413,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -4423,7 +4431,7 @@
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -4435,12 +4443,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4463,16 +4471,16 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4522,7 +4530,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -4540,7 +4548,7 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
@@ -4554,10 +4562,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4580,19 +4588,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4641,7 +4649,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -4659,7 +4667,7 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4673,10 +4681,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4699,16 +4707,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4734,13 +4742,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4758,7 +4766,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -4776,7 +4784,7 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4790,10 +4798,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4816,16 +4824,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4875,7 +4883,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -4893,13 +4901,13 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -4907,14 +4915,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4933,17 +4941,17 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4992,7 +5000,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -5010,13 +5018,13 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5024,10 +5032,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5050,17 +5058,17 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5085,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5109,7 +5117,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -5136,15 +5144,15 @@
         <v>20</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5170,13 +5178,13 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5202,13 +5210,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5226,7 +5234,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -5258,10 +5266,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5284,13 +5292,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5341,7 +5349,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -5353,7 +5361,7 @@
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5373,10 +5381,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5399,13 +5407,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5456,7 +5464,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -5488,14 +5496,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5517,13 +5525,13 @@
         <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5573,7 +5581,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -5605,14 +5613,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5634,16 +5642,16 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5692,7 +5700,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -5724,10 +5732,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5753,13 +5761,13 @@
         <v>89</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5809,7 +5817,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5841,10 +5849,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5870,13 +5878,13 @@
         <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5926,7 +5934,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -5935,7 +5943,7 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
@@ -5958,10 +5966,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5984,13 +5992,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6041,7 +6049,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -6050,7 +6058,7 @@
         <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
@@ -6073,10 +6081,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6099,13 +6107,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6156,7 +6164,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -6188,10 +6196,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6217,10 +6225,10 @@
         <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6247,13 +6255,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6271,7 +6279,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6303,10 +6311,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6329,16 +6337,16 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6388,7 +6396,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6420,10 +6428,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6446,13 +6454,13 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6503,7 +6511,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -6512,7 +6520,7 @@
         <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>99</v>
@@ -6535,10 +6543,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6561,13 +6569,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6618,7 +6626,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -6650,14 +6658,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6679,13 +6687,13 @@
         <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6735,7 +6743,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -6767,14 +6775,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6796,16 +6804,16 @@
         <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6854,7 +6862,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -6886,10 +6894,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6915,10 +6923,10 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6945,13 +6953,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -6969,7 +6977,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7001,10 +7009,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7027,13 +7035,13 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7084,7 +7092,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7116,10 +7124,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7142,16 +7150,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7201,7 +7209,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -7210,7 +7218,7 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
@@ -7233,10 +7241,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7262,13 +7270,13 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7294,13 +7302,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7318,7 +7326,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7327,7 +7335,7 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>99</v>
@@ -7350,10 +7358,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7376,16 +7384,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7435,7 +7443,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -7444,7 +7452,7 @@
         <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
@@ -7467,10 +7475,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7496,13 +7504,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7528,13 +7536,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7552,7 +7560,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -7584,10 +7592,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7610,13 +7618,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7667,7 +7675,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -7676,10 +7684,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -7699,10 +7707,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7725,13 +7733,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7782,7 +7790,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -7814,14 +7822,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7843,13 +7851,13 @@
         <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7899,7 +7907,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -7931,14 +7939,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7960,16 +7968,16 @@
         <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8018,7 +8026,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -8050,10 +8058,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8076,13 +8084,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8133,7 +8141,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8142,10 +8150,10 @@
         <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8160,15 +8168,15 @@
         <v>20</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8191,13 +8199,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8248,7 +8256,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -8257,10 +8265,10 @@
         <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -8280,10 +8288,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8306,13 +8314,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8363,7 +8371,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -8395,14 +8403,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8424,13 +8432,13 @@
         <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8480,7 +8488,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -8512,14 +8520,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8541,16 +8549,16 @@
         <v>132</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8599,7 +8607,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -8631,10 +8639,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8657,13 +8665,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8714,7 +8722,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8741,17 +8749,17 @@
         <v>20</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AO61">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
